--- a/セリフ編集/その他セリフ/01-試合本編・勝利演出.xlsx
+++ b/セリフ編集/その他セリフ/01-試合本編・勝利演出.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I256"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[1]</t>
+          <t xml:space="preserve">normal.normal[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="5">
@@ -2137,14 +2137,14 @@
       </c>
       <c r="G60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…！</t>
+          <t xml:space="preserve">くっ…まだ…まだだ…！</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[2]</t>
+          <t xml:space="preserve">normal.normal[2]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="5">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="G61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">効いた…けど…負けない…！</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[3]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[3]</t>
+          <t xml:space="preserve">normal.normal[3]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="5">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="G62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">はぁ…はぁ…立てる…まだ…</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[4]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2218,29 +2218,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[4]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">earnest.normal[1]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁっ…！</t>
+          <t xml:space="preserve">ぐっ…！ まだ…立てる…！</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2250,29 +2250,29 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[1]</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">earnest.normal[2]</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きゃっ…！</t>
+          <t xml:space="preserve">くぅ…っ！ 効いた…けど…！</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[3]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2282,29 +2282,29 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[2]</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">earnest.normal[3]</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">はぁ…はぁ…負けるもんか…！</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2314,29 +2314,29 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[3]</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">bold.normal[1]</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">はっ…やるじゃん…でもまだだよ！</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[4]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2346,29 +2346,29 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[4]</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">bold.normal[2]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひっ…！</t>
+          <t xml:space="preserve">この程度じゃ…倒れないよ！</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[3]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2378,29 +2378,29 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[1]</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">bold.normal[3]</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あぁんっ…！</t>
+          <t xml:space="preserve">あはは…痛い痛い…でもね！</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2410,29 +2410,29 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[2]</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">easygoing.normal[1]</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んっ…！</t>
+          <t xml:space="preserve">あたた…でもまだ大丈夫！</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2442,29 +2442,29 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[3]</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">easygoing.normal[2]</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅ…っ！</t>
+          <t xml:space="preserve">う〜ん…効いたかも…でもへーきへーき！</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[4]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[3]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2474,29 +2474,29 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[4]</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">easygoing.normal[3]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ…っ！</t>
+          <t xml:space="preserve">いたた…ちょっと休憩…なんてね！</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">quiet.normal[1]</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぐはっ…！</t>
+          <t xml:space="preserve">……まだ</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2538,29 +2538,29 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">quiet.normal[2]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がっ…！</t>
+          <t xml:space="preserve">……これくらい</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2570,29 +2570,29 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[3]</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">quiet.normal[3]</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…！</t>
+          <t xml:space="preserve">……立てる</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[4]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2602,29 +2602,29 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[4]</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">shy.normal[1]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うあっ…！</t>
+          <t xml:space="preserve">い、痛い…でも…まだ…</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2634,29 +2634,29 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">shy.normal[2]</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きゃあっ…！</t>
+          <t xml:space="preserve">う、うぅ…でも…立てる…から…</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[3]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2666,29 +2666,29 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">shy.normal[3]</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">ひっ…で、でも…負けたくない…</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2698,29 +2698,29 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[3]</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">emotional.normal[1]</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">痛いっ…！ でも…でもっ…！</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[4]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2730,29 +2730,29 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[4]</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">emotional.normal[2]</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああっ…！</t>
+          <t xml:space="preserve">うぅっ…こんなので…負けないっ…！</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[3]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2762,29 +2762,29 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[1]</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">emotional.normal[3]</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ！</t>
+          <t xml:space="preserve">泣かない…泣かないよ…まだ…！</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,24 +2799,24 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[2]</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">normal[1]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ</t>
+          <t xml:space="preserve">くっ…！</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[3]</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">normal[2]</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くっ</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[4]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[3]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[4]</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">normal[3]</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[4]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[1]</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">normal[4]</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ</t>
+          <t xml:space="preserve">はぁっ…！</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,24 +2927,24 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[2]</t>
+          <t xml:space="preserve">polite[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ…っ</t>
+          <t xml:space="preserve">きゃっ…！</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,24 +2959,24 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[3]</t>
+          <t xml:space="preserve">polite[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くっ</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[4]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[3]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,666 +2991,711 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[4]</t>
+          <t xml:space="preserve">polite[3]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はぁ…っ</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[4]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[1]</t>
+          <t xml:space="preserve">polite[4]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが見たかったんだよ！ 最高の試合だった！</t>
+          <t xml:space="preserve">ひっ…！</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[2]</t>
+          <t xml:space="preserve">seductive[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待通り…いや、期待以上の名勝負だった！</t>
+          <t xml:space="preserve">あぁんっ…！</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[3]</t>
+          <t xml:space="preserve">seductive[2]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">会場が一つになった瞬間だった…！</t>
+          <t xml:space="preserve">んっ…！</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[4]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[3]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[4]</t>
+          <t xml:space="preserve">seductive[3]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの声が選手に届いた試合だった</t>
+          <t xml:space="preserve">くぅ…っ！</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[5]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[4]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[5]</t>
+          <t xml:space="preserve">seductive[4]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">歴史に残るカードを実現してくれた！</t>
+          <t xml:space="preserve">はぁ…っ！</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badCrowd[1]</t>
+          <t xml:space="preserve">delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し噛み合ってほしかった…</t>
+          <t xml:space="preserve">ぐはっ…！</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badCrowd[2]</t>
+          <t xml:space="preserve">delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待が大きすぎたのかもしれない</t>
+          <t xml:space="preserve">がっ…！</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[3]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badCrowd[3]</t>
+          <t xml:space="preserve">delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそ本当の名勝負を見せてほしい</t>
+          <t xml:space="preserve">くそっ…！</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[4]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[4]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badCrowd[4]</t>
+          <t xml:space="preserve">delinquent[4]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カードは最高だったのに…内容が追いつかなかった</t>
+          <t xml:space="preserve">うあっ…！</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの声が聞こえてたよ</t>
+          <t xml:space="preserve">きゃあっ…！</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられたなら…嬉しい</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[3]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相手に最高の舞台。感謝しかない</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[4]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">ojousama[4]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合、絶対に負けられなかった</t>
+          <t xml:space="preserve">ああっ…！</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">cool[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの歓声が力になった。最高だ！</t>
+          <t xml:space="preserve">…っ！</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.quiet._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">cool[2]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（観客に向かって静かに頭を下げる）</t>
+          <t xml:space="preserve">……っ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.shy._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[3]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">cool[3]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…皆さんの声が…聞こえてて…嬉しかった…です</t>
+          <t xml:space="preserve">…くっ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[4]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">cool[4]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなありがとー！ 最高の試合だったよ！</t>
+          <t xml:space="preserve">…っ…</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">composed[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられたなら嬉しいです</t>
+          <t xml:space="preserve">…っ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">composed[2]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声援が力になりました。ありがとうございます</t>
+          <t xml:space="preserve">ふ…っ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.emotional._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[3]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">composed[3]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの声が……聞こえてた……ありがとう……！（涙）</t>
+          <t xml:space="preserve">…くっ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[4]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">composed[4]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれたはず</t>
+          <t xml:space="preserve">…はぁ…っ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal._default[2]</t>
+          <t xml:space="preserve">atk.normal.normal[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="5">
@@ -3660,29 +3705,29 @@
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この結果じゃ満足できない</t>
+          <t xml:space="preserve">いくよ！</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal._default[3]</t>
+          <t xml:space="preserve">atk.normal.normal[2]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="5">
@@ -3692,701 +3737,701 @@
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれたのに…悔しい</t>
+          <t xml:space="preserve">まだまだ！</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[3]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">atk.normal.normal[3]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっといい試合にする。約束する</t>
+          <t xml:space="preserve">負けないから！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[4]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">atk.normal.normal[4]</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんじゃ足りない。もっとやれる</t>
+          <t xml:space="preserve">ここからよ！</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.quiet._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">atk.bold.normal[1]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（悔しそうに俯く）</t>
+          <t xml:space="preserve">まだまだっ！</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.shy._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">atk.bold.normal[2]</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…もっと…頑張れたのに…</t>
+          <t xml:space="preserve">ここからが本番よっ！</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[3]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">atk.bold.normal[3]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うーん…もっとやれたなあ。ごめんね</t>
+          <t xml:space="preserve">逃がさないわよ！</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[4]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">atk.bold.normal[4]</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださったのに…申し訳ありません</t>
+          <t xml:space="preserve">受けてみなさい！</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">atk.quiet.normal[1]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそもっといい試合にします</t>
+          <t xml:space="preserve">…まだ、終わらない</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.emotional._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[2]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">atk.quiet.normal[2]</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめん……もっとやれたのに……悔しい……！</t>
+          <t xml:space="preserve">…ここからよ</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[3]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">atk.quiet.normal[3]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取った</t>
+          <t xml:space="preserve">…負けるわけにはいかない</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[4]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">atk.quiet.normal[4]</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">atk.earnest.normal[1]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで一勝</t>
+          <t xml:space="preserve">絶対に…勝つ！</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[2]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">atk.earnest.normal[2]</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…決まったわね</t>
+          <t xml:space="preserve">ここで引くわけにはいかない！</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[3]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">atk.earnest.normal[3]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然よ！</t>
+          <t xml:space="preserve">全力で…いく！</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[4]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">atk.earnest.normal[4]</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなもんよ！</t>
+          <t xml:space="preserve">諦めない…！</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">atk.emotional.normal[1]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの勝ち！</t>
+          <t xml:space="preserve">負けたくないっ…！</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">atk.emotional.normal[2]</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った</t>
+          <t xml:space="preserve">絶対に…絶対にっ…！</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[3]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">atk.emotional.normal[3]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（小さく頷く）</t>
+          <t xml:space="preserve">うぅっ…でも、負けないっ…！</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[4]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[1]</t>
+          <t xml:space="preserve">atk.emotional.normal[4]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="10">
         <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…！</t>
+          <t xml:space="preserve">こんなところで…終われないっ！</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">atk.easygoing.normal[1]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本当に…ありがとうございます！</t>
+          <t xml:space="preserve">あはは、楽しくなってきた！</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">atk.easygoing.normal[2]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…やった…！</t>
+          <t xml:space="preserve">いい試合にしようよ！</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[3]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">atk.easygoing.normal[3]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った…勝ったよ…！</t>
+          <t xml:space="preserve">まだまだいけるよ〜！</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[4]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[1]</t>
+          <t xml:space="preserve">atk.easygoing.normal[4]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="9">
@@ -4396,93 +4441,93 @@
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、勝てちゃった</t>
+          <t xml:space="preserve">本気出しちゃうよ？</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">atk.shy.normal[1]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、ラッキー♪</t>
+          <t xml:space="preserve">あ、あの…いきますっ…!</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">atk.shy.normal[2]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったよ〜</t>
+          <t xml:space="preserve">わ、わたし…まだまだ…!</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[3]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy._default[1]</t>
+          <t xml:space="preserve">atk.shy.normal[3]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="8">
@@ -4492,29 +4537,29 @@
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…か、勝った…</t>
+          <t xml:space="preserve">ま、負けたくないから…!</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[4]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.shy._default[2]</t>
+          <t xml:space="preserve">atk.shy.normal[4]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="8">
@@ -4524,29 +4569,29 @@
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（深々とお辞儀）</t>
+          <t xml:space="preserve">こ、ここから…ですっ…!</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.normal.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[1]</t>
+          <t xml:space="preserve">climax.normal.normal[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="5">
@@ -4556,29 +4601,29 @@
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい</t>
+          <t xml:space="preserve">（…ここからだ）</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.normal.normal[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[2]</t>
+          <t xml:space="preserve">climax.normal.normal[2]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="5">
@@ -4588,669 +4633,669 @@
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだまだね</t>
+          <t xml:space="preserve">（負けない…！）</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.bold.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">climax.bold.normal[1]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は勝つわ</t>
+          <t xml:space="preserve">（ここからが、あたしの時間！）</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.bold.normal[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">climax.bold.normal[2]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…完敗ね</t>
+          <t xml:space="preserve">（さあ…決めにいく）</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.quiet.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">climax.quiet.normal[1]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘でしょ？</t>
+          <t xml:space="preserve">（…集中。今だけは、何も考えなくていい）</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.quiet.normal[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">climax.quiet.normal[2]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなはずじゃ…</t>
+          <t xml:space="preserve">（…身体が軽い。いける）</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.earnest.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">climax.earnest.normal[1]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は絶対に！</t>
+          <t xml:space="preserve">（ここまで来た…あとは、出し切るだけ）</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.earnest.normal[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">climax.earnest.normal[2]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けた</t>
+          <t xml:space="preserve">（全部…全部出し切る）</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.emotional.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">climax.emotional.normal[1]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（俯く）</t>
+          <t xml:space="preserve">（胸が苦しい…でも、この痛みが、生きてる証だから）</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.emotional.normal[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[1]</t>
+          <t xml:space="preserve">climax.emotional.normal[2]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="10">
         <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は必ず勝ちます</t>
+          <t xml:space="preserve">（お願い、身体…もう少しだけ動いて）</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">climax.easygoing.normal[1]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい、もっと強くなる</t>
+          <t xml:space="preserve">（わくわくする…この瞬間が一番好き）</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.normal[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">climax.easygoing.normal[2]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい…悔しいよ…</t>
+          <t xml:space="preserve">（最高の試合にしよう！）</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.shy.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">climax.shy.normal[1]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんで…なんで負けたの…</t>
+          <t xml:space="preserve">（…ま、まだ…いけるはず…!）</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.shy.normal[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">climax.shy.normal[2]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けちゃった</t>
+          <t xml:space="preserve">（こ、ここで…決めなきゃ…!）</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">bigmove.normal.normal[1]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次がんばろ</t>
+          <t xml:space="preserve">いくよ…これで決める！</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[2]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">bigmove.normal.normal[2]</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">むぅ…悔しいなあ</t>
+          <t xml:space="preserve">ここで…終わりだ！</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[3]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">bigmove.normal.normal[3]</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご、ごめんなさい…</t>
+          <t xml:space="preserve">全部出し切る…！</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">bigmove.earnest.normal[1]</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（消え入りそう）</t>
+          <t xml:space="preserve">絶対に…ここで決める！</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[2]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">bigmove.earnest.normal[2]</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">噂は聞いていたわ</t>
+          <t xml:space="preserve">全力で…いきます！</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[3]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">bigmove.earnest.normal[3]</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">初めまして…よろしく</t>
+          <t xml:space="preserve">負けたくない…だから…！</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">bigmove.bold.normal[1]</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一度やってみたかった</t>
+          <t xml:space="preserve">さあ…終わらせるわよっ！</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">bigmove.bold.normal[2]</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こうして向かい合えるとは</t>
+          <t xml:space="preserve">見せてあげる…わたしの全力！</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[3]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">bigmove.bold.normal[3]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -5260,125 +5305,125 @@
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと当たれるな！</t>
+          <t xml:space="preserve">思いっきりいくわよっ！！</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">bigmove.easygoing.normal[1]</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってたぞ、この日を</t>
+          <t xml:space="preserve">よーし、ここで決めちゃおう！</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">bigmove.easygoing.normal[2]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気で来いよ</t>
+          <t xml:space="preserve">いっくよー！ 最後の大技！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[3]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">bigmove.easygoing.normal[3]</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく</t>
+          <t xml:space="preserve">えへへ…全力いくよー！</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">bigmove.quiet.normal[1]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="7">
@@ -5388,300 +5433,2943 @@
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（軽く頭を下げる）</t>
+          <t xml:space="preserve">……いく</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">bigmove.quiet.normal[2]</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします！</t>
+          <t xml:space="preserve">……これで</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[3]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">bigmove.quiet.normal[3]</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦、全力で挑みます</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">bigmove.shy.normal[1]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと…ずっとやりたかった！</t>
+          <t xml:space="preserve">あ、あの…いきます…！</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">bigmove.shy.normal[2]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢だったの、これ！</t>
+          <t xml:space="preserve">こ、ここで…決めます…！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[3]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">bigmove.shy.normal[3]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、やっとだね</t>
+          <t xml:space="preserve">が、頑張ります…！</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">bigmove.emotional.normal[1]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくー！</t>
+          <t xml:space="preserve">うぅっ…絶対に…決めるんだ…！</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">bigmove.emotional.normal[2]</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、楽しみだったよ</t>
+          <t xml:space="preserve">泣かない…泣かないから…いくよ！</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.shy._default[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[3]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">bigmove.emotional.normal[3]</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…よ、よろしく…</t>
+          <t xml:space="preserve">ここで…ここでっ…！</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[1]</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodCrowd[1]</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これが見たかったんだよ！ 最高の試合だった！</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[2]</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodCrowd[2]</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待通り…いや、期待以上の名勝負だった！</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[3]</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodCrowd[3]</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">会場が一つになった瞬間だった…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[4]</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodCrowd[4]</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ファンの声が選手に届いた試合だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[5]</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodCrowd[5]</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">歴史に残るカードを実現してくれた！</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[1]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badCrowd[1]</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう少し噛み合ってほしかった…</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[2]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badCrowd[2]</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待が大きすぎたのかもしれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[3]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badCrowd[3]</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次こそ本当の名勝負を見せてほしい</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[4]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badCrowd[4]</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">カードは最高だったのに…内容が追いつかなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなの声が聞こえてたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待に応えられたなら…嬉しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の相手に最高の舞台。感謝しかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この試合、絶対に負けられなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの歓声が力になった。最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（観客に向かって静かに頭を下げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…皆さんの声が…聞こえてて…嬉しかった…です</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなありがとー！ 最高の試合だったよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待に応えられたなら嬉しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声援が力になりました。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">goodWinner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなの声が……聞こえてた……ありがとう……！（涙）</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだやれたはず</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この結果じゃ満足できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">応援してくれたのに…悔しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はもっといい試合にする。約束する</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんなんじゃ足りない。もっとやれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（悔しそうに俯く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんなさい…もっと…頑張れたのに…</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うーん…もっとやれたなあ。ごめんね</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">応援してくださったのに…申し訳ありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次こそもっといい試合にします</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">badWinner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめん……もっとやれたのに……悔しい……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…取った</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これで一勝</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[4]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.normal._default[4]</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅ…決まったわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然よ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんなもんよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[3]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.bold._default[3]</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしの勝ち！</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（小さく頷く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本当に…ありがとうございます！</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった…やった…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った…勝ったよ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いやー、勝てちゃった</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふっ、ラッキー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったよ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…か、勝った…</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">winner.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（深々とお辞儀）</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだまだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…次は勝つわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[4]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.normal._default[4]</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…完敗ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…嘘でしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こんなはずじゃ…</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[3]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.bold._default[3]</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…次は絶対に！</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けた</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（俯く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…次は必ず勝ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい、もっと強くなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい…悔しいよ…</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…なんで…なんで負けたの…</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あちゃー、負けちゃった</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…次がんばろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">むぅ…悔しいなあ</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご、ごめんなさい…</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">loser.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（消え入りそう）</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">噂は聞いていたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">初めまして…よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一度やってみたかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[4]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal._default[4]</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こうして向かい合えるとは</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やっと当たれるな！</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">待ってたぞ、この日を</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[3]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold._default[3]</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本気で来いよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（軽く頭を下げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この一戦、全力で挑みます</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと…ずっとやりたかった！</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">夢だったの、これ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いやー、やっとだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よろしくー！</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing._default[3]</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふっ、楽しみだったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…よ、よろしく…</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">FIRST_MEET_LINES.shy._default[2]</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr" s="2">
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr" s="12">
+      <c r="D256" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">shy._default[2]</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr" s="8">
+      <c r="F256" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">内気</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr" s="3">
+      <c r="G256" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……よろしくお願いします…</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I172"/>
+  <autoFilter ref="A1:I256"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/01-試合本編・勝利演出.xlsx
+++ b/セリフ編集/その他セリフ/01-試合本編・勝利演出.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I256"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal._default[1]</t>
+          <t xml:space="preserve">direct._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal._default[2]</t>
+          <t xml:space="preserve">direct._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal._default[3]</t>
+          <t xml:space="preserve">direct._default.normal[3]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="5">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.bold[1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold._default[1]</t>
+          <t xml:space="preserve">direct._default.bold[1]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.bold[2]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold._default[2]</t>
+          <t xml:space="preserve">direct._default.bold[2]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="6">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.bold[3]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold._default[3]</t>
+          <t xml:space="preserve">direct._default.bold[3]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="6">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.quiet[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet._default[1]</t>
+          <t xml:space="preserve">direct._default.quiet[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="7">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.quiet._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.quiet[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.quiet._default[2]</t>
+          <t xml:space="preserve">direct._default.quiet[2]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="7">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.shy._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.shy[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.shy._default[1]</t>
+          <t xml:space="preserve">direct._default.shy[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="8">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.shy._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.shy[2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.shy._default[2]</t>
+          <t xml:space="preserve">direct._default.shy[2]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="8">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing._default[1]</t>
+          <t xml:space="preserve">direct._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="9">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing._default[2]</t>
+          <t xml:space="preserve">direct._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="9">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.earnest[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest._default[1]</t>
+          <t xml:space="preserve">direct._default.earnest[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="10">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.earnest[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest._default[2]</t>
+          <t xml:space="preserve">direct._default.earnest[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="10">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.earnest[3]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest._default[3]</t>
+          <t xml:space="preserve">direct._default.earnest[3]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="10">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.emotional._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.emotional[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.emotional._default[1]</t>
+          <t xml:space="preserve">direct._default.emotional[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="10">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.emotional._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.emotional[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.emotional._default[2]</t>
+          <t xml:space="preserve">direct._default.emotional[2]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="10">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.emotional._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct._default.emotional[3]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.emotional._default[3]</t>
+          <t xml:space="preserve">direct._default.emotional[3]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="10">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.normal[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal._default[1]</t>
+          <t xml:space="preserve">competition_won._default.normal[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="5">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.normal[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal._default[2]</t>
+          <t xml:space="preserve">competition_won._default.normal[2]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="5">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.normal[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal._default[3]</t>
+          <t xml:space="preserve">competition_won._default.normal[3]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="5">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal._default[4]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.normal[4]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal._default[4]</t>
+          <t xml:space="preserve">competition_won._default.normal[4]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="5">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal._default[5]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.normal[5]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal._default[5]</t>
+          <t xml:space="preserve">competition_won._default.normal[5]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="5">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.bold[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold._default[1]</t>
+          <t xml:space="preserve">competition_won._default.bold[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="6">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.bold[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold._default[2]</t>
+          <t xml:space="preserve">competition_won._default.bold[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="6">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.bold[3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold._default[3]</t>
+          <t xml:space="preserve">competition_won._default.bold[3]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="6">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold._default[4]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.bold[4]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold._default[4]</t>
+          <t xml:space="preserve">competition_won._default.bold[4]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="6">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold._default[5]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.bold[5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold._default[5]</t>
+          <t xml:space="preserve">competition_won._default.bold[5]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="6">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.quiet[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet._default[1]</t>
+          <t xml:space="preserve">competition_won._default.quiet[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="7">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.quiet._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.quiet[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.quiet._default[2]</t>
+          <t xml:space="preserve">competition_won._default.quiet[2]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="7">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.shy._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.shy[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.shy._default[1]</t>
+          <t xml:space="preserve">competition_won._default.shy[1]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="8">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.shy._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.shy[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.shy._default[2]</t>
+          <t xml:space="preserve">competition_won._default.shy[2]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="8">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing._default[1]</t>
+          <t xml:space="preserve">competition_won._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="9">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing._default[2]</t>
+          <t xml:space="preserve">competition_won._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="9">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing._default[3]</t>
+          <t xml:space="preserve">competition_won._default.easygoing[3]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="9">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing._default[4]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.easygoing[4]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing._default[4]</t>
+          <t xml:space="preserve">competition_won._default.easygoing[4]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="9">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.earnest[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest._default[1]</t>
+          <t xml:space="preserve">competition_won._default.earnest[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="10">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.earnest[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest._default[2]</t>
+          <t xml:space="preserve">competition_won._default.earnest[2]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="10">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.earnest[3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest._default[3]</t>
+          <t xml:space="preserve">competition_won._default.earnest[3]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="10">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.emotional._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.emotional[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.emotional._default[1]</t>
+          <t xml:space="preserve">competition_won._default.emotional[1]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="10">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.emotional._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won._default.emotional[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.emotional._default[2]</t>
+          <t xml:space="preserve">competition_won._default.emotional[2]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.normal[1]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="5">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.normal[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.normal[2]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="5">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.normal[3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal._default[3]</t>
+          <t xml:space="preserve">fa_signing._default.normal[3]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="5">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.bold[1]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="6">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.bold[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.bold[2]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="6">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.bold[3]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold._default[3]</t>
+          <t xml:space="preserve">fa_signing._default.bold[3]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="6">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.quiet[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.quiet[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="7">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.quiet._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.quiet[2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.quiet._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.quiet[2]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="7">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.shy._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.shy[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.shy._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.shy[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="8">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.shy._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.shy[2]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.shy._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.shy[2]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="8">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="9">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="9">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.earnest[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.earnest[1]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="10">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.earnest[2]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.earnest[2]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="10">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest._default[3]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.earnest[3]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest._default[3]</t>
+          <t xml:space="preserve">fa_signing._default.earnest[3]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="10">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.emotional._default[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.emotional[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.emotional._default[1]</t>
+          <t xml:space="preserve">fa_signing._default.emotional[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="10">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.emotional._default[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing._default.emotional[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.emotional._default[2]</t>
+          <t xml:space="preserve">fa_signing._default.emotional[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="10">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.standard[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2122,29 +2122,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.normal[1]</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…まだ…まだだ…！</t>
+          <t xml:space="preserve">くっ…！</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.standard[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2154,29 +2154,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.normal[2]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[2]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">効いた…けど…負けない…！</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.standard[3]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2186,29 +2186,29 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.normal[3]</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[3]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ…はぁ…立てる…まだ…</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.standard[4]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2218,29 +2218,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.normal[1]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">standard[4]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぐっ…！ まだ…立てる…！</t>
+          <t xml:space="preserve">はぁっ…！</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2250,29 +2250,29 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.normal[2]</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">polite[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅ…っ！ 効いた…けど…！</t>
+          <t xml:space="preserve">きゃっ…！</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2282,29 +2282,29 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.normal[3]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">polite[2]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ…はぁ…負けるもんか…！</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[3]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2314,29 +2314,29 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.normal[1]</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">polite[3]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ…やるじゃん…でもまだだよ！</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[4]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2346,29 +2346,29 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.normal[2]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">polite[4]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度じゃ…倒れないよ！</t>
+          <t xml:space="preserve">ひっ…！</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2378,29 +2378,29 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.normal[3]</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">seductive[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…痛い痛い…でもね！</t>
+          <t xml:space="preserve">あぁんっ…！</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2410,29 +2410,29 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.normal[1]</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">seductive[2]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたた…でもまだ大丈夫！</t>
+          <t xml:space="preserve">んっ…！</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2442,29 +2442,29 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.normal[2]</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">seductive[3]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…効いたかも…でもへーきへーき！</t>
+          <t xml:space="preserve">くぅ…っ！</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[4]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2474,29 +2474,29 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.normal[3]</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">seductive[4]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いたた…ちょっと休憩…なんてね！</t>
+          <t xml:space="preserve">はぁ…っ！</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.normal[1]</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ</t>
+          <t xml:space="preserve">ぐはっ…！</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2538,29 +2538,29 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.normal[2]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これくらい</t>
+          <t xml:space="preserve">がっ…！</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.quiet.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2570,29 +2570,29 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.normal[3]</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……立てる</t>
+          <t xml:space="preserve">くそっ…！</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[4]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2602,29 +2602,29 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.normal[1]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">delinquent[4]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">い、痛い…でも…まだ…</t>
+          <t xml:space="preserve">うあっ…！</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2634,29 +2634,29 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.normal[2]</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う、うぅ…でも…立てる…から…</t>
+          <t xml:space="preserve">きゃあっ…！</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.shy.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2666,29 +2666,29 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy.normal[3]</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひっ…で、でも…負けたくない…</t>
+          <t xml:space="preserve">あっ…！</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2698,29 +2698,29 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.normal[1]</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛いっ…！ でも…でもっ…！</t>
+          <t xml:space="preserve">うぅっ…！</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[4]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2730,29 +2730,29 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.normal[2]</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">ojousama[4]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…こんなので…負けないっ…！</t>
+          <t xml:space="preserve">ああっ…！</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2762,29 +2762,29 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.normal[3]</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">cool[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">泣かない…泣かないよ…まだ…！</t>
+          <t xml:space="preserve">…っ！</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,24 +2799,24 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[1]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">cool[2]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…！</t>
+          <t xml:space="preserve">……っ</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[2]</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">cool[3]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">…くっ</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[4]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[3]</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">cool[4]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">…っ…</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.normal[4]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[4]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">composed[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁっ…！</t>
+          <t xml:space="preserve">…っ</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,24 +2927,24 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[1]</t>
+          <t xml:space="preserve">composed[2]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きゃっ…！</t>
+          <t xml:space="preserve">ふ…っ</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[3]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,24 +2959,24 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[2]</t>
+          <t xml:space="preserve">composed[3]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">…くっ</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[4]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,711 +2991,666 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[3]</t>
+          <t xml:space="preserve">composed[4]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">…はぁ…っ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.polite[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[4]</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">goodCrowd[1]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひっ…！</t>
+          <t xml:space="preserve">これが見たかったんだよ！ 最高の試合だった！</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[1]</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">goodCrowd[2]</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あぁんっ…！</t>
+          <t xml:space="preserve">期待通り…いや、期待以上の名勝負だった！</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[3]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[2]</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">goodCrowd[3]</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んっ…！</t>
+          <t xml:space="preserve">会場が一つになった瞬間だった…！</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[4]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[3]</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">goodCrowd[4]</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くぅ…っ！</t>
+          <t xml:space="preserve">ファンの声が選手に届いた試合だった</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.seductive[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[5]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[4]</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">goodCrowd[5]</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ…っ！</t>
+          <t xml:space="preserve">歴史に残るカードを実現してくれた！</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">badCrowd[1]</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぐはっ…！</t>
+          <t xml:space="preserve">もう少し噛み合ってほしかった…</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">badCrowd[2]</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がっ…！</t>
+          <t xml:space="preserve">期待が大きすぎたのかもしれない</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[3]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[3]</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">badCrowd[3]</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…！</t>
+          <t xml:space="preserve">次こそ本当の名勝負を見せてほしい</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.delinquent[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[4]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[4]</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">badCrowd[4]</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うあっ…！</t>
+          <t xml:space="preserve">カードは最高だったのに…内容が追いつかなかった</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.normal[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">goodWinner._default.normal[1]</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きゃあっ…！</t>
+          <t xml:space="preserve">みんなの声が聞こえてたよ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.normal[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">goodWinner._default.normal[2]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっ…！</t>
+          <t xml:space="preserve">期待に応えられたなら…嬉しい</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.normal[3]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[3]</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">goodWinner._default.normal[3]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…！</t>
+          <t xml:space="preserve">最高の相手に最高の舞台。感謝しかない</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.ojousama[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[4]</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">goodWinner._default.bold[1]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああっ…！</t>
+          <t xml:space="preserve">この試合、絶対に負けられなかった</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.bold[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[1]</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">goodWinner._default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ！</t>
+          <t xml:space="preserve">あの歓声が力になった。最高だ！</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[2]</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">goodWinner._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ</t>
+          <t xml:space="preserve">………（観客に向かって静かに頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.shy[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[3]</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">goodWinner._default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くっ</t>
+          <t xml:space="preserve">あ、あの…皆さんの声が…聞こえてて…嬉しかった…です</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.cool[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[4]</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">goodWinner._default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…</t>
+          <t xml:space="preserve">みんなありがとー！ 最高の試合だったよ！</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[1]</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">goodWinner._default.earnest[1]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ</t>
+          <t xml:space="preserve">期待に応えられたなら嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.earnest[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[2]</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">goodWinner._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふ…っ</t>
+          <t xml:space="preserve">声援が力になりました。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[3]</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">goodWinner._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くっ</t>
+          <t xml:space="preserve">みんなの声が……聞こえてた……ありがとう……！（涙）</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES.composed[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DAMAGE_VOICE_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[4]</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">badWinner._default.normal[1]</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はぁ…っ</t>
+          <t xml:space="preserve">…まだやれたはず</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.normal[2]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.normal[1]</t>
+          <t xml:space="preserve">badWinner._default.normal[2]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="5">
@@ -3705,29 +3660,29 @@
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いくよ！</t>
+          <t xml:space="preserve">この結果じゃ満足できない</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.normal[3]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.normal[2]</t>
+          <t xml:space="preserve">badWinner._default.normal[3]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="5">
@@ -3737,701 +3692,701 @@
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ！</t>
+          <t xml:space="preserve">応援してくれたのに…悔しい</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.normal[3]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">badWinner._default.bold[1]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けないから！</t>
+          <t xml:space="preserve">次はもっといい試合にする。約束する</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.normal[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.bold[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.normal[4]</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">badWinner._default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからよ！</t>
+          <t xml:space="preserve">こんなんじゃ足りない。もっとやれる</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.normal[1]</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">badWinner._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだっ！</t>
+          <t xml:space="preserve">………（悔しそうに俯く）</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.shy[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.normal[2]</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">badWinner._default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからが本番よっ！</t>
+          <t xml:space="preserve">ごめんなさい…もっと…頑張れたのに…</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[3]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.normal[3]</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">badWinner._default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃がさないわよ！</t>
+          <t xml:space="preserve">うーん…もっとやれたなあ。ごめんね</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.normal[4]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.normal[4]</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">badWinner._default.earnest[1]</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けてみなさい！</t>
+          <t xml:space="preserve">応援してくださったのに…申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.earnest[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.normal[1]</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">badWinner._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、終わらない</t>
+          <t xml:space="preserve">次こそもっといい試合にします</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.normal[2]</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">badWinner._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここからよ</t>
+          <t xml:space="preserve">ごめん……もっとやれたのに……悔しい……！</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.normal[3]</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">winner._default.normal[1]</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けるわけにはいかない</t>
+          <t xml:space="preserve">…取った</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.normal[4]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.normal[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.normal[4]</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">winner._default.normal[2]</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて</t>
+          <t xml:space="preserve">勝ったわ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.normal[3]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.normal[1]</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">winner._default.normal[3]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…勝つ！</t>
+          <t xml:space="preserve">これで一勝</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.normal[4]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.normal[2]</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">winner._default.normal[4]</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで引くわけにはいかない！</t>
+          <t xml:space="preserve">ふぅ…決まったわね</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.normal[3]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">winner._default.bold[1]</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で…いく！</t>
+          <t xml:space="preserve">当然よ！</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.normal[4]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.bold[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.normal[4]</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">winner._default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">諦めない…！</t>
+          <t xml:space="preserve">こんなもんよ！</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.bold[3]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.normal[1]</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">winner._default.bold[3]</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないっ…！</t>
+          <t xml:space="preserve">わたしの勝ち！</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.normal[2]</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">winner._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…絶対にっ…！</t>
+          <t xml:space="preserve">…勝った</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.quiet[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.normal[3]</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">winner._default.quiet[2]</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…でも、負けないっ…！</t>
+          <t xml:space="preserve">……（小さく頷く）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.normal[4]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.normal[4]</t>
+          <t xml:space="preserve">winner._default.earnest[1]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="10">
         <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで…終われないっ！</t>
+          <t xml:space="preserve">勝てました…！</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.earnest[2]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.normal[1]</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">winner._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、楽しくなってきた！</t>
+          <t xml:space="preserve">本当に…ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.emotional[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.normal[2]</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">winner._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合にしようよ！</t>
+          <t xml:space="preserve">やった…やった…！</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.emotional[2]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.normal[3]</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">winner._default.emotional[2]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだいけるよ〜！</t>
+          <t xml:space="preserve">勝った…勝ったよ…！</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.normal[4]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.normal[4]</t>
+          <t xml:space="preserve">winner._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="9">
@@ -4441,93 +4396,93 @@
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気出しちゃうよ？</t>
+          <t xml:space="preserve">いやー、勝てちゃった</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.normal[1]</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">winner._default.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…いきますっ…!</t>
+          <t xml:space="preserve">ふふっ、ラッキー♪</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.normal[2]</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">winner._default.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、わたし…まだまだ…!</t>
+          <t xml:space="preserve">勝ったよ〜</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.shy[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.normal[3]</t>
+          <t xml:space="preserve">winner._default.shy[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="8">
@@ -4537,29 +4492,29 @@
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、負けたくないから…!</t>
+          <t xml:space="preserve">…か、勝った…</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.shy.normal[4]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner._default.shy[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.shy.normal[4]</t>
+          <t xml:space="preserve">winner._default.shy[2]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="8">
@@ -4569,29 +4524,29 @@
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここから…ですっ…!</t>
+          <t xml:space="preserve">……（深々とお辞儀）</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.normal[1]</t>
+          <t xml:space="preserve">loser._default.normal[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="5">
@@ -4601,29 +4556,29 @@
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…ここからだ）</t>
+          <t xml:space="preserve">…悔しい</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.normal[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.normal[2]</t>
+          <t xml:space="preserve">loser._default.normal[2]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="5">
@@ -4633,669 +4588,669 @@
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（負けない…！）</t>
+          <t xml:space="preserve">…まだまだね</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.normal[3]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.normal[1]</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">loser._default.normal[3]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここからが、あたしの時間！）</t>
+          <t xml:space="preserve">…次は勝つわ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.normal[4]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.normal[2]</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">loser._default.normal[4]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（さあ…決めにいく）</t>
+          <t xml:space="preserve">…完敗ね</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.normal[1]</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">loser._default.bold[1]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…集中。今だけは、何も考えなくていい）</t>
+          <t xml:space="preserve">…嘘でしょ？</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.bold[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.normal[2]</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">loser._default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…身体が軽い。いける）</t>
+          <t xml:space="preserve">こんなはずじゃ…</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.bold[3]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.normal[1]</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">loser._default.bold[3]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここまで来た…あとは、出し切るだけ）</t>
+          <t xml:space="preserve">…次は絶対に！</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.normal[2]</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">loser._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（全部…全部出し切る）</t>
+          <t xml:space="preserve">…負けた</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.quiet[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.normal[1]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">loser._default.quiet[2]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（胸が苦しい…でも、この痛みが、生きてる証だから）</t>
+          <t xml:space="preserve">……（俯く）</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.normal[2]</t>
+          <t xml:space="preserve">loser._default.earnest[1]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="10">
         <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（お願い、身体…もう少しだけ動いて）</t>
+          <t xml:space="preserve">…次は必ず勝ちます</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.earnest[2]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.normal[1]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">loser._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（わくわくする…この瞬間が一番好き）</t>
+          <t xml:space="preserve">…悔しい、もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.normal[2]</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">loser._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（最高の試合にしよう！）</t>
+          <t xml:space="preserve">…悔しい…悔しいよ…</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.shy.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.emotional[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.shy.normal[1]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">loser._default.emotional[2]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…ま、まだ…いけるはず…!）</t>
+          <t xml:space="preserve">…なんで…なんで負けたの…</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.shy.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.shy.normal[2]</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">loser._default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（こ、ここで…決めなきゃ…!）</t>
+          <t xml:space="preserve">あちゃー、負けちゃった</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.normal[1]</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">loser._default.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いくよ…これで決める！</t>
+          <t xml:space="preserve">…次がんばろ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.normal[2]</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">loser._default.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで…終わりだ！</t>
+          <t xml:space="preserve">むぅ…悔しいなあ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.normal[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.shy[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.normal[3]</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">loser._default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全部出し切る…！</t>
+          <t xml:space="preserve">…ご、ごめんなさい…</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser._default.shy[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.normal[1]</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">loser._default.shy[2]</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…ここで決める！</t>
+          <t xml:space="preserve">……（消え入りそう）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.normal[2]</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">_default.normal[1]</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で…いきます！</t>
+          <t xml:space="preserve">噂は聞いていたわ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.normal[3]</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">_default.normal[2]</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくない…だから…！</t>
+          <t xml:space="preserve">初めまして…よろしく</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.normal[1]</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">_default.normal[3]</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ…終わらせるわよっ！</t>
+          <t xml:space="preserve">一度やってみたかった</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.normal[4]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.normal[2]</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">_default.normal[4]</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見せてあげる…わたしの全力！</t>
+          <t xml:space="preserve">こうして向かい合えるとは</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.normal[3]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -5305,125 +5260,125 @@
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">思いっきりいくわよっ！！</t>
+          <t xml:space="preserve">やっと当たれるな！</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.normal[1]</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">_default.bold[2]</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、ここで決めちゃおう！</t>
+          <t xml:space="preserve">待ってたぞ、この日を</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.normal[2]</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">_default.bold[3]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いっくよー！ 最後の大技！</t>
+          <t xml:space="preserve">本気で来いよ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.normal[3]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ…全力いくよー！</t>
+          <t xml:space="preserve">…よろしく</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.normal[1]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="7">
@@ -5433,270 +5388,270 @@
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いく</t>
+          <t xml:space="preserve">……（軽く頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.normal[2]</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これで</t>
+          <t xml:space="preserve">よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.normal[3]</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりだ</t>
+          <t xml:space="preserve">この一戦、全力で挑みます</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.normal[1]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、あの…いきます…！</t>
+          <t xml:space="preserve">ずっと…ずっとやりたかった！</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.normal[2]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、ここで…決めます…！</t>
+          <t xml:space="preserve">夢だったの、これ！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.shy.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.shy.normal[3]</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">が、頑張ります…！</t>
+          <t xml:space="preserve">いやー、やっとだね</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.normal[1]</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅっ…絶対に…決めるんだ…！</t>
+          <t xml:space="preserve">よろしくー！</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.normal[2]</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">泣かない…泣かないから…いくよ！</t>
+          <t xml:space="preserve">ふふっ、楽しみだったよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.normal[3]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/battle-engine-main.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CUTIN_LINES</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.normal[3]</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">_default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで…ここでっ…！</t>
+          <t xml:space="preserve">あ、あの…よ、よろしく…</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5706,2670 +5661,27 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
+          <t xml:space="preserve">FIRST_MEET_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodCrowd[1]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが見たかったんだよ！ 最高の試合だった！</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="40" customHeight="1">
-      <c r="A173" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[2]</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodCrowd[2]</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">期待通り…いや、期待以上の名勝負だった！</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="40" customHeight="1">
-      <c r="A174" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[3]</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodCrowd[3]</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">会場が一つになった瞬間だった…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="40" customHeight="1">
-      <c r="A175" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[4]</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodCrowd[4]</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ファンの声が選手に届いた試合だった</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="40" customHeight="1">
-      <c r="A176" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodCrowd[5]</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodCrowd[5]</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">歴史に残るカードを実現してくれた！</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[1]</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badCrowd[1]</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">もう少し噛み合ってほしかった…</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="40" customHeight="1">
-      <c r="A178" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[2]</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badCrowd[2]</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">期待が大きすぎたのかもしれない</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="40" customHeight="1">
-      <c r="A179" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[3]</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badCrowd[3]</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">次こそ本当の名勝負を見せてほしい</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="40" customHeight="1">
-      <c r="A180" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badCrowd[4]</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badCrowd[4]</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">カードは最高だったのに…内容が追いつかなかった</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="40" customHeight="1">
-      <c r="A181" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">みんなの声が聞こえてたよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="40" customHeight="1">
-      <c r="A182" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">期待に応えられたなら…嬉しい</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="40" customHeight="1">
-      <c r="A183" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">最高の相手に最高の舞台。感謝しかない</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="40" customHeight="1">
-      <c r="A184" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この試合、絶対に負けられなかった</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="40" customHeight="1">
-      <c r="A185" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あの歓声が力になった。最高だ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="40" customHeight="1">
-      <c r="A186" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">………（観客に向かって静かに頭を下げる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="40" customHeight="1">
-      <c r="A187" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、あの…皆さんの声が…聞こえてて…嬉しかった…です</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="40" customHeight="1">
-      <c r="A188" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">みんなありがとー！ 最高の試合だったよ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="40" customHeight="1">
-      <c r="A189" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">期待に応えられたなら嬉しいです</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="40" customHeight="1">
-      <c r="A190" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">声援が力になりました。ありがとうございます</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="40" customHeight="1">
-      <c r="A191" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">goodWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">みんなの声が……聞こえてた……ありがとう……！（涙）</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="40" customHeight="1">
-      <c r="A192" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…まだやれたはず</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="40" customHeight="1">
-      <c r="A193" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この結果じゃ満足できない</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="40" customHeight="1">
-      <c r="A194" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">応援してくれたのに…悔しい</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="40" customHeight="1">
-      <c r="A195" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">次はもっといい試合にする。約束する</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="40" customHeight="1">
-      <c r="A196" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こんなんじゃ足りない。もっとやれる</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="40" customHeight="1">
-      <c r="A197" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">………（悔しそうに俯く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="40" customHeight="1">
-      <c r="A198" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ごめんなさい…もっと…頑張れたのに…</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="40" customHeight="1">
-      <c r="A199" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">うーん…もっとやれたなあ。ごめんね</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="40" customHeight="1">
-      <c r="A200" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">応援してくださったのに…申し訳ありません</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="40" customHeight="1">
-      <c r="A201" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">次こそもっといい試合にします</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="40" customHeight="1">
-      <c r="A202" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">badWinner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ごめん……もっとやれたのに……悔しい……！</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="40" customHeight="1">
-      <c r="A203" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…取った</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="40" customHeight="1">
-      <c r="A204" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝ったわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="40" customHeight="1">
-      <c r="A205" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">これで一勝</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="40" customHeight="1">
-      <c r="A206" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふぅ…決まったわね</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="40" customHeight="1">
-      <c r="A207" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">当然よ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="40" customHeight="1">
-      <c r="A208" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こんなもんよ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="40" customHeight="1">
-      <c r="A209" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたしの勝ち！</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="40" customHeight="1">
-      <c r="A210" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…勝った</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="40" customHeight="1">
-      <c r="A211" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……（小さく頷く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="40" customHeight="1">
-      <c r="A212" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝てました…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="40" customHeight="1">
-      <c r="A213" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">本当に…ありがとうございます！</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="40" customHeight="1">
-      <c r="A214" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">やった…やった…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="40" customHeight="1">
-      <c r="A215" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝った…勝ったよ…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="40" customHeight="1">
-      <c r="A216" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">いやー、勝てちゃった</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="40" customHeight="1">
-      <c r="A217" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふっ、ラッキー♪</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="40" customHeight="1">
-      <c r="A218" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝ったよ〜</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="40" customHeight="1">
-      <c r="A219" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…か、勝った…</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="40" customHeight="1">
-      <c r="A220" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">winner.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……（深々とお辞儀）</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="40" customHeight="1">
-      <c r="A221" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…悔しい</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="40" customHeight="1">
-      <c r="A222" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…まだまだね</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="40" customHeight="1">
-      <c r="A223" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…次は勝つわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="40" customHeight="1">
-      <c r="A224" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…完敗ね</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="40" customHeight="1">
-      <c r="A225" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…嘘でしょ？</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="40" customHeight="1">
-      <c r="A226" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こんなはずじゃ…</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="40" customHeight="1">
-      <c r="A227" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…次は絶対に！</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="40" customHeight="1">
-      <c r="A228" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…負けた</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="40" customHeight="1">
-      <c r="A229" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……（俯く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="40" customHeight="1">
-      <c r="A230" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…次は必ず勝ちます</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="40" customHeight="1">
-      <c r="A231" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…悔しい、もっと強くなる</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="40" customHeight="1">
-      <c r="A232" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…悔しい…悔しいよ…</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="40" customHeight="1">
-      <c r="A233" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なんで…なんで負けたの…</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="40" customHeight="1">
-      <c r="A234" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あちゃー、負けちゃった</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="40" customHeight="1">
-      <c r="A235" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…次がんばろ</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="40" customHeight="1">
-      <c r="A236" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">むぅ…悔しいなあ</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="40" customHeight="1">
-      <c r="A237" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ご、ごめんなさい…</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="40" customHeight="1">
-      <c r="A238" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">loser.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……（消え入りそう）</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="40" customHeight="1">
-      <c r="A239" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">噂は聞いていたわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="40" customHeight="1">
-      <c r="A240" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">初めまして…よろしく</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="40" customHeight="1">
-      <c r="A241" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">一度やってみたかった</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="40" customHeight="1">
-      <c r="A242" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal._default[4]</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal._default[4]</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こうして向かい合えるとは</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="40" customHeight="1">
-      <c r="A243" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">やっと当たれるな！</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="40" customHeight="1">
-      <c r="A244" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">待ってたぞ、この日を</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="40" customHeight="1">
-      <c r="A245" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold._default[3]</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold._default[3]</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">本気で来いよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="40" customHeight="1">
-      <c r="A246" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…よろしく</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="40" customHeight="1">
-      <c r="A247" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet._default[2]</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……（軽く頭を下げる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="40" customHeight="1">
-      <c r="A248" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">よろしくお願いします！</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="40" customHeight="1">
-      <c r="A249" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この一戦、全力で挑みます</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="40" customHeight="1">
-      <c r="A250" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ずっと…ずっとやりたかった！</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="40" customHeight="1">
-      <c r="A251" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">夢だったの、これ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="40" customHeight="1">
-      <c r="A252" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">いやー、やっとだね</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="40" customHeight="1">
-      <c r="A253" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">よろしくー！</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="40" customHeight="1">
-      <c r="A254" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふっ、楽しみだったよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="40" customHeight="1">
-      <c r="A255" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あ、あの…よ、よろしく…</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="40" customHeight="1">
-      <c r="A256" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FIRST_MEET_LINES</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">……よろしくお願いします…</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I256"/>
+  <autoFilter ref="A1:I172"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
